--- a/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -318,16 +318,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -453,7 +453,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -515,7 +515,7 @@
     <t>健康保険における被保険者証番号の枝番を示す拡張</t>
   </si>
   <si>
-    <t>健康保険における被保険者証番号を示す拡張。2桁の全角数字文字列。一桁の場合には先頭に０をつけて2桁にする。</t>
+    <t>健康保険における被保険者証番号を示す拡張。2桁の半角数字文字列。一桁の場合には先頭に0をつけて2桁にする。</t>
   </si>
   <si>
     <t>Coverage.modifierExtension</t>
@@ -552,37 +552,328 @@
     <t>Business Identifier for the coverage　このカバレッジに割り当てられた一意の識別子【詳細参照】</t>
   </si>
   <si>
-    <t>A unique identifier assigned to this coverage.  
-このカバレッジに割り当てられた一意の識別子。</t>
+    <t>A unique identifier assigned to this coverage.  このカバレッジに割り当てられた一意の識別子。</t>
+  </si>
+  <si>
+    <t>Allows coverages to be distinguished and referenced.  
+カバレッジを区別して参照できるようにする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>IN1-2</t>
+  </si>
+  <si>
+    <t>C.32, C.33, C.39</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子　例）00012345:あいう:１８７:05</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
+  </si>
+  <si>
+    <t>「被保険者個人識別子」の文字列仕様を参照のこと</t>
+  </si>
+  <si>
+    <t>カバレッジを区別し、参照することができます。 / Allows coverages to be distinguished and referenced.</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.use</t>
+  </si>
+  <si>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.system</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.system</t>
+  </si>
+  <si>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/clins/Idsystem/JP_Insurance_memberID</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.value</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.value</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
+本仕様では、以下、これを「被保険者個人識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
+被保険者個人識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
+要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者個人識別子」の文字列仕様を参照のこと</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
+  </si>
+  <si>
+    <t>保険者情報を設定</t>
+  </si>
+  <si>
+    <t>保険者情報として[JP_Organization](StructureDefinition-jp-organization.html)を設定する。</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者識別子（CSV形式）　"00012345","１２－３４","５６７８","00"</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報を囲み文字をダブルクォーテーション、区切りをカンマにて連結する</t>
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
 カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
-ルール："{被保険者記号}","{被保険者番号}","{枝番}"  
-例："１２－３４","５６７８","００"</t>
-  </si>
-  <si>
-    <t>Allows coverages to be distinguished and referenced.  
-カバレッジを区別して参照できるようにする。</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>C02</t>
-  </si>
-  <si>
-    <t>IN1-2</t>
-  </si>
-  <si>
-    <t>C.32, C.33, C.39</t>
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/JP_Coverage_id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.value</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。</t>
+  </si>
+  <si>
+    <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
+カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+【JP Core仕様】保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"
+要素を省略する、とある場合には、長さ０の文字列とする。</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>保険者情報</t>
+  </si>
+  <si>
+    <t>健康保険等の保険者情報を設定する。[JP_Organization](StructureDefinition-jp-organization.html)をリソースにて表現する</t>
   </si>
   <si>
     <t>Coverage.status</t>
@@ -603,9 +894,6 @@
 「ドラフト」リソースはさらに編集される可能性があり、「アクティブ」リソースは不変であり、ステータスが「キャンセル」に変更されるだけである可能性があるため、リソースのステータスを追跡する必要がある。</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>リソースインスタンスの状態を指定するコード。 / A code specifying the state of the resource instance.</t>
   </si>
   <si>
@@ -622,10 +910,6 @@
   </si>
   <si>
     <t>Coverage.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Coverage category such as medical or accident　医療保険や事故補償のような分類</t>
@@ -637,7 +921,7 @@
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
 すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。  
-【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”urn:oid:1.2.392.100495.20.2.61”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
+【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
   </si>
   <si>
     <t>The order of application of coverages is dependent on the types of coverage.  
@@ -713,10 +997,6 @@
   </si>
   <si>
     <t>Coverage.subscriberId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>ID assigned to the subscriber　被保険者に割り当てられたID</t>
@@ -730,8 +1010,8 @@
 保険者は、連絡や請求（デジタルおよびその他）でこの識別子を要求する。  
 保険会社は、通信および請求（デジタルおよびその他）でこの識別子を要求する。  
 【JP Core仕様】被保険者記号と番号を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
-ルール："{被保険者記号}","{被保険者番号}"  
-例："１２－３４","５６７８"</t>
+ルール：{被保険者記号}:{被保険者番号}  
+例："あいう","５６７８"</t>
   </si>
   <si>
     <t>Coverage.beneficiary</t>
@@ -778,7 +1058,7 @@
 一部の補償では、単一の識別子が加入者に発行され、次に一意の従属番号が各受益者に発行される。  
 一部の保険では、単一の識別子が加入者に発行され、その後、各受益者に固有の扶養番号が発行される。  
 【JP Core仕様】医療保険で本リソースを使用する場合には、この要素に拡張 InsuredPersonSubNumberに設定した値と同じ、被保険者番号の枝番号全角2桁を設定する。  
-例："００"</t>
+例："00"</t>
   </si>
   <si>
     <t>C17</t>
@@ -803,14 +1083,11 @@
   <si>
     <t>To determine relationship between the patient and the subscriber to determine coordination of benefits.  
 患者と加入者の関係を決定し、給付の調整を決定する。  
-【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される被保険者区分コード（system=”urn:oid:1.2.392.100495.20.2.62”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１２が使用できる。  
+【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される被保険者区分コード（system=”http://jpfhir.jp/fhir/core/mhlw/CodeSystem/InsuredPersonCategory”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１２が使用できる。  
 　1 被保険者  
 　2 被扶養者</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
@@ -821,10 +1098,6 @@
   </si>
   <si>
     <t>Coverage.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>カバレッジの開始日と終了日 / Coverage start and end dates</t>
@@ -867,7 +1140,7 @@
 </t>
   </si>
   <si>
-    <t>ポリシーの発行者 / Issuer of the policy</t>
+    <t>支払者に関する情報</t>
   </si>
   <si>
     <t>The program or plan underwriter or payor including both insurance and non-insurance agreements, such as patient-pay agreements.  
@@ -921,28 +1194,7 @@
     <t>Coverage.class.id</t>
   </si>
   <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Coverage.class.extension</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Coverage.class.modifierExtension</t>
@@ -1128,9 +1380,6 @@
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.coding</t>
@@ -1734,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP58"/>
+  <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.57421875" customWidth="true" bestFit="true"/>
@@ -1773,7 +2022,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.53125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="59.44921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="51.2734375" customWidth="true" bestFit="true"/>
@@ -3387,10 +3636,10 @@
         <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3427,16 +3676,14 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>168</v>
@@ -3477,15 +3724,17 @@
         <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>90</v>
@@ -3494,25 +3743,25 @@
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3537,13 +3786,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3561,13 +3810,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3576,30 +3825,30 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3619,23 +3868,19 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3659,13 +3904,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3695,22 +3940,22 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3718,21 +3963,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3741,23 +3986,21 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3793,57 +4036,57 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3860,25 +4103,25 @@
         <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3903,13 +4146,13 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3927,7 +4170,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3945,27 +4188,27 @@
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3988,17 +4231,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4023,13 +4268,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -4047,7 +4292,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4065,19 +4310,19 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -4085,7 +4330,7 @@
         <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4108,7 +4353,7 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>224</v>
@@ -4127,7 +4372,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>80</v>
@@ -4169,10 +4414,10 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>90</v>
@@ -4184,30 +4429,30 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4215,7 +4460,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>90</v>
@@ -4230,20 +4475,18 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4291,7 +4534,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4309,16 +4552,16 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4326,10 +4569,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4349,23 +4592,19 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4389,13 +4628,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4413,7 +4652,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4431,16 +4670,16 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4448,10 +4687,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4474,20 +4713,18 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4535,7 +4772,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4550,13 +4787,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4573,18 +4810,20 @@
         <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4596,7 +4835,7 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>256</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>257</v>
@@ -4608,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>260</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4657,10 +4896,10 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>82</v>
@@ -4672,30 +4911,30 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>263</v>
+        <v>178</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4706,7 +4945,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -4718,20 +4957,16 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4779,25 +5014,25 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4814,21 +5049,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4840,15 +5075,17 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>195</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4885,37 +5122,37 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -4932,44 +5169,46 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>202</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -4993,13 +5232,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5017,25 +5256,25 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -5044,7 +5283,7 @@
         <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5052,45 +5291,45 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5115,13 +5354,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -5139,25 +5378,25 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
@@ -5166,7 +5405,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5174,10 +5413,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5200,26 +5439,26 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>286</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>289</v>
+        <v>227</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>80</v>
@@ -5237,13 +5476,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -5261,10 +5500,10 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -5279,7 +5518,7 @@
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
@@ -5288,7 +5527,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5296,10 +5535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5322,20 +5561,18 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5383,10 +5620,10 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>90</v>
@@ -5401,27 +5638,27 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5444,18 +5681,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>242</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>243</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5503,7 +5738,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5521,27 +5756,27 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>248</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5564,20 +5799,18 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5625,7 +5858,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5643,7 +5876,7 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>253</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
@@ -5652,7 +5885,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5660,10 +5893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5671,7 +5904,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -5680,23 +5913,25 @@
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>218</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5721,13 +5956,13 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5745,10 +5980,10 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5760,16 +5995,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -5780,21 +6015,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5803,22 +6038,22 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5843,13 +6078,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -5867,13 +6102,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -5888,13 +6123,13 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5902,10 +6137,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5925,19 +6160,23 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>218</v>
+        <v>293</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -5985,7 +6224,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5997,44 +6236,44 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6043,21 +6282,23 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6105,80 +6346,78 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>166</v>
+        <v>311</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6227,45 +6466,45 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6273,7 +6512,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -6288,19 +6527,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6325,13 +6564,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6349,10 +6588,10 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>90</v>
@@ -6364,30 +6603,30 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6407,19 +6646,23 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6467,7 +6710,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6479,22 +6722,22 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6502,21 +6745,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6528,18 +6771,20 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6563,55 +6808,55 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6636,7 +6881,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6648,19 +6893,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6709,13 +6954,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -6724,13 +6969,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6755,10 +7000,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6767,19 +7012,23 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>218</v>
+        <v>344</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6827,49 +7076,49 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6888,18 +7137,20 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>135</v>
+        <v>354</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>277</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>278</v>
+        <v>356</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6935,19 +7186,19 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>279</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6959,13 +7210,13 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6982,10 +7233,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7005,23 +7256,19 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>189</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7069,7 +7316,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>191</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7081,13 +7328,13 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>192</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7096,7 +7343,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7104,21 +7351,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7127,19 +7374,19 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>195</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>355</v>
+        <v>196</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>356</v>
+        <v>165</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7189,25 +7436,25 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>198</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>358</v>
+        <v>192</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7216,7 +7463,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7224,45 +7471,45 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>363</v>
+        <v>165</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>364</v>
+        <v>166</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7317,19 +7564,19 @@
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>366</v>
+        <v>133</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7338,7 +7585,7 @@
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7346,10 +7593,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7357,7 +7604,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7372,17 +7619,19 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7407,13 +7656,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7431,10 +7680,10 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>90</v>
@@ -7449,7 +7698,7 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7458,7 +7707,7 @@
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7466,10 +7715,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7477,7 +7726,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7492,19 +7741,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7553,10 +7802,10 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7571,27 +7820,27 @@
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7614,19 +7863,17 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7675,7 +7922,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7693,27 +7940,27 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7721,7 +7968,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
@@ -7736,19 +7983,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7797,10 +8044,10 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>90</v>
@@ -7821,21 +8068,21 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7846,7 +8093,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7855,20 +8102,20 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>320</v>
+        <v>394</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7917,13 +8164,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -7941,7 +8188,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -7952,21 +8199,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7978,16 +8225,20 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>272</v>
+        <v>398</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8035,25 +8286,25 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>274</v>
+        <v>396</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -8077,14 +8328,14 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8096,17 +8347,15 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8155,25 +8404,25 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8197,7 +8446,7 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>281</v>
+        <v>162</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8210,26 +8459,24 @@
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>283</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8277,7 +8524,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8295,7 +8542,7 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8319,36 +8566,38 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>363</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>407</v>
+        <v>166</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8373,13 +8622,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>408</v>
+        <v>80</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8397,25 +8646,25 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>365</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8432,10 +8681,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8458,17 +8707,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8493,13 +8744,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8517,7 +8768,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8552,10 +8803,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8578,20 +8829,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>376</v>
+        <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>416</v>
+        <v>189</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8639,7 +8886,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>415</v>
+        <v>191</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8651,13 +8898,13 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -8674,14 +8921,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8700,20 +8947,18 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>421</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>422</v>
+        <v>195</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>423</v>
+        <v>196</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8749,19 +8994,19 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>198</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8773,25 +9018,2199 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AO58" t="s" s="2">
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AP58" t="s" s="2">
-        <v>210</v>
+      <c r="M62" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -280,7 +280,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -879,7 +879,7 @@
     <t>Coverage.status</t>
   </si>
   <si>
-    <t>アクティブ|キャンセル|ドラフト|エラーに入った / active | cancelled | draft | entered-in-error</t>
+    <t>アクティブ|キャンセル|ドラフト|エラー入力 / active | cancelled | draft | entered-in-error</t>
   </si>
   <si>
     <t>The status of the resource instance.  

--- a/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
@@ -1986,17 +1986,17 @@
   <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.57421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="21.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="128.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="110.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2005,28 +2005,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="207.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.84375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.3046875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.69140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="59.44921875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="51.2734375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="62.85546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="50.96484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="43.95703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="53.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
@@ -372,7 +372,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -700,7 +700,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -931,7 +931,7 @@
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-type|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -1091,7 +1091,7 @@
     <t>加入者と受益者（被保険者/対象当事者/患者）の関係。 / The relationship between the Subscriber and the Beneficiary (insured/covered party/patient).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship</t>
+    <t>http://hl7.org/fhir/ValueSet/subscriber-relationship|4.0.1</t>
   </si>
   <si>
     <t>C03</t>
@@ -1236,7 +1236,7 @@
     <t>ポリシー分類、例。グループ、プラン、クラスなど / The policy classifications, eg. Group, Plan, Class, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-class</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-class|4.0.1</t>
   </si>
   <si>
     <t>Coverage.class.value</t>
@@ -1373,7 +1373,7 @@
     <t>患者の自己負担が指定されているサービスの種類。 / The types of services to which patient copayments are specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.type.id</t>
@@ -1564,7 +1564,7 @@
     <t>Coverage.costToBeneficiary.value[x]</t>
   </si>
   <si>
-    <t>Quantity {SimpleQuantity}
+    <t>Quantity {SimpleQuantity|4.0.1}
 Money</t>
   </si>
   <si>
@@ -1622,7 +1622,7 @@
     <t>部品からの例外の種類またはCopaysなどの財務義務の完全な価値。 / The types of exceptions from the part or full value of financial obligations such as copays.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
+    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception|4.0.1</t>
   </si>
   <si>
     <t>Coverage.costToBeneficiary.exception.period</t>
@@ -1660,7 +1660,7 @@
     <t>Coverage.contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Contract)
+    <t xml:space="preserve">Reference(Contract|4.0.1)
 </t>
   </si>
   <si>
@@ -2011,7 +2011,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="177.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.83203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-coverage.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
